--- a/Result/profitability/3631.xlsx
+++ b/Result/profitability/3631.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15</v>
+        <v>0.13625</v>
       </c>
       <c r="N2" t="n">
-        <v>23.80875</v>
+        <v>24.08</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -774,7 +774,7 @@
         <v>1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30375</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -889,7 +889,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.31625</v>
+        <v>0.31125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1004,7 +1004,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4625</v>
+        <v>0.49</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1121,7 +1121,7 @@
         <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67375</v>
+        <v>0.65625</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1246,7 +1246,7 @@
         <v>1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8450000000000001</v>
+        <v>0.8274999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1369,7 +1369,7 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9087500000000001</v>
+        <v>0.9025</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9552,6 +9552,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-313.04%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>13</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.16375</v>
+      </c>
+      <c r="N73" t="n">
+        <v>22.4875</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-0.05000000000000002</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-2.860000000000001</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.1576626240352812</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.5238095238095237</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.1673032849503437</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
